--- a/data/trans_bre/POLIPATOLOGIA_2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 14,86</t>
+          <t>0,25; 14,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 25,59</t>
+          <t>10,87; 27,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 24,97</t>
+          <t>8,07; 24,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 12,14</t>
+          <t>-1,83; 12,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 93,86</t>
+          <t>1,08; 95,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,76; 133,5</t>
+          <t>40,2; 139,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,64; 117,18</t>
+          <t>27,61; 117,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 49,42</t>
+          <t>-5,61; 52,59</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 28,16</t>
+          <t>16,73; 28,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 19,57</t>
+          <t>7,89; 19,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 18,9</t>
+          <t>7,62; 19,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 19,89</t>
+          <t>7,84; 19,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,35; 181,21</t>
+          <t>78,6; 181,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 110,23</t>
+          <t>33,03; 108,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 99,22</t>
+          <t>29,29; 98,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 87,28</t>
+          <t>25,27; 87,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 21,01</t>
+          <t>7,28; 20,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 16,03</t>
+          <t>0,8; 15,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 19,63</t>
+          <t>6,87; 19,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 17,61</t>
+          <t>3,99; 17,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,69; 156,97</t>
+          <t>36,57; 152,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 64,52</t>
+          <t>1,65; 61,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,47; 121,15</t>
+          <t>30,94; 122,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 55,5</t>
+          <t>10,72; 56,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 16,52</t>
+          <t>3,53; 16,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 26,93</t>
+          <t>13,39; 26,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 21,25</t>
+          <t>7,3; 20,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 35,72</t>
+          <t>4,33; 37,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,21; 91,74</t>
+          <t>14,06; 92,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,32; 134,86</t>
+          <t>49,36; 132,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 83,36</t>
+          <t>21,75; 82,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 110,75</t>
+          <t>10,54; 118,53</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 26,0</t>
+          <t>10,21; 25,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 39,82</t>
+          <t>21,8; 40,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,6; 26,39</t>
+          <t>9,43; 26,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 22,83</t>
+          <t>-10,96; 23,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,83; 277,63</t>
+          <t>61,55; 280,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,94; 175,42</t>
+          <t>63,7; 176,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,9; 141,97</t>
+          <t>33,48; 142,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 72,53</t>
+          <t>-27,44; 74,31</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 25,01</t>
+          <t>9,61; 24,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 21,97</t>
+          <t>5,0; 21,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 18,53</t>
+          <t>2,01; 18,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 13,86</t>
+          <t>-0,68; 14,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,63; 165,53</t>
+          <t>39,98; 159,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,76; 77,11</t>
+          <t>13,64; 76,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 93,45</t>
+          <t>7,12; 93,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 36,75</t>
+          <t>-1,38; 37,26</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 14,85</t>
+          <t>5,53; 15,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 17,94</t>
+          <t>7,58; 17,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 15,4</t>
+          <t>5,83; 16,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,74; 47,38</t>
+          <t>19,3; 48,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,09; 87,3</t>
+          <t>25,73; 88,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,05; 74,73</t>
+          <t>25,99; 72,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,05; 79,71</t>
+          <t>23,72; 81,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,78; 133,97</t>
+          <t>45,55; 133,97</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 16,67</t>
+          <t>7,43; 17,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 14,86</t>
+          <t>6,11; 14,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 13,96</t>
+          <t>4,21; 13,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 31,1</t>
+          <t>9,34; 29,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,02; 74,49</t>
+          <t>27,09; 75,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,57; 84,15</t>
+          <t>28,02; 82,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,0; 57,52</t>
+          <t>13,91; 57,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,92; 304,56</t>
+          <t>32,98; 286,75</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,95</t>
+          <t>11,6; 15,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,79</t>
+          <t>12,32; 16,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,89; 14,35</t>
+          <t>9,9; 14,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,5; 28,84</t>
+          <t>13,35; 29,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,65; 84,85</t>
+          <t>55,88; 83,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,38; 72,08</t>
+          <t>48,55; 71,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,02; 62,54</t>
+          <t>39,74; 63,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41,68; 109,04</t>
+          <t>40,34; 110,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>5,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 14,54</t>
+          <t>0,51; 14,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 27,03</t>
+          <t>10,75; 25,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 24,41</t>
+          <t>9,57; 24,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 12,65</t>
+          <t>-0,75; 12,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 95,05</t>
+          <t>2,36; 94,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,2; 139,34</t>
+          <t>39,03; 132,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,61; 117,22</t>
+          <t>32,33; 121,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 52,59</t>
+          <t>-2,5; 51,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>13,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 28,0</t>
+          <t>16,49; 27,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 19,63</t>
+          <t>7,91; 19,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 19,25</t>
+          <t>7,75; 19,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 19,91</t>
+          <t>7,37; 18,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,6; 181,64</t>
+          <t>79,68; 177,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 108,81</t>
+          <t>32,89; 116,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,29; 98,82</t>
+          <t>29,85; 96,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,27; 87,9</t>
+          <t>25,62; 84,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,3</t>
+          <t>11,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 20,57</t>
+          <t>7,25; 20,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 15,23</t>
+          <t>0,37; 15,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 19,9</t>
+          <t>6,45; 19,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 17,8</t>
+          <t>4,78; 17,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,57; 152,38</t>
+          <t>36,04; 157,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 61,04</t>
+          <t>1,19; 63,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,94; 122,94</t>
+          <t>28,75; 123,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 56,25</t>
+          <t>11,9; 55,94</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,96</t>
+          <t>14,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 16,61</t>
+          <t>4,12; 16,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,39; 26,74</t>
+          <t>13,44; 26,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 20,94</t>
+          <t>7,09; 20,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 37,89</t>
+          <t>6,15; 21,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 92,47</t>
+          <t>16,74; 96,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,36; 132,91</t>
+          <t>47,82; 130,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 82,29</t>
+          <t>22,58; 82,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,54; 118,53</t>
+          <t>16,3; 77,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,37</t>
+          <t>20,81</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 25,85</t>
+          <t>9,94; 26,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,8; 40,78</t>
+          <t>22,1; 39,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,43; 26,39</t>
+          <t>8,66; 25,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 23,26</t>
+          <t>12,68; 27,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,55; 280,84</t>
+          <t>59,87; 287,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,7; 176,64</t>
+          <t>65,25; 169,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,48; 142,67</t>
+          <t>30,24; 134,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 74,31</t>
+          <t>36,56; 102,87</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 24,31</t>
+          <t>10,12; 25,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,0; 21,5</t>
+          <t>5,19; 21,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,15</t>
+          <t>3,42; 18,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 14,25</t>
+          <t>-0,24; 14,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,98; 159,82</t>
+          <t>44,82; 172,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 76,18</t>
+          <t>13,99; 76,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 93,4</t>
+          <t>12,32; 94,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 37,26</t>
+          <t>-0,68; 35,99</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,38</t>
+          <t>21,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 15,07</t>
+          <t>5,66; 14,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,58; 17,66</t>
+          <t>7,6; 18,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 16,09</t>
+          <t>5,96; 15,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,3; 48,29</t>
+          <t>16,31; 27,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,73; 88,24</t>
+          <t>25,46; 87,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,99; 72,6</t>
+          <t>25,79; 75,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,72; 81,77</t>
+          <t>24,75; 80,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,55; 133,97</t>
+          <t>37,05; 73,69</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,81</t>
+          <t>10,74</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,43; 17,14</t>
+          <t>7,43; 17,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 14,53</t>
+          <t>5,65; 14,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,93</t>
+          <t>4,6; 13,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 29,0</t>
+          <t>6,75; 15,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,09; 75,1</t>
+          <t>26,64; 78,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,02; 82,54</t>
+          <t>25,38; 83,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,91; 57,08</t>
+          <t>16,39; 58,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,98; 286,75</t>
+          <t>23,56; 63,91</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,87</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,6; 15,67</t>
+          <t>11,49; 15,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,69</t>
+          <t>12,27; 16,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,9; 14,47</t>
+          <t>10,1; 14,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,35; 29,39</t>
+          <t>11,45; 15,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,88; 83,27</t>
+          <t>55,13; 84,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,55; 71,48</t>
+          <t>48,18; 71,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,74; 63,23</t>
+          <t>40,48; 62,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40,34; 110,2</t>
+          <t>33,85; 51,75</t>
         </is>
       </c>
     </row>
